--- a/Spark/Data/Simulated/Bruno/sumary_general_SIM2.xlsx
+++ b/Spark/Data/Simulated/Bruno/sumary_general_SIM2.xlsx
@@ -416,19 +416,19 @@
         <v>1000</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7212</v>
+        <v>0.406616666666667</v>
       </c>
       <c r="E2" t="n">
-        <v>0.209724925901869</v>
+        <v>0.255797743424559</v>
       </c>
       <c r="F2" t="n">
-        <v>0.740196781245307</v>
+        <v>0.417680122242813</v>
       </c>
       <c r="G2" t="n">
-        <v>0.689823904370416</v>
+        <v>0.389251213267002</v>
       </c>
       <c r="H2" t="n">
-        <v>0.260240981660521</v>
+        <v>0.582368884155207</v>
       </c>
     </row>
     <row r="3">
@@ -442,19 +442,19 @@
         <v>1000</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7164</v>
+        <v>0.400066666666667</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2112254998037</v>
+        <v>0.244502441022351</v>
       </c>
       <c r="F3" t="n">
-        <v>0.731687156395326</v>
+        <v>0.410353037824878</v>
       </c>
       <c r="G3" t="n">
-        <v>0.689615075880487</v>
+        <v>0.381050758597494</v>
       </c>
       <c r="H3" t="n">
-        <v>0.314074237735059</v>
+        <v>0.617412564612235</v>
       </c>
     </row>
     <row r="4">
@@ -468,19 +468,19 @@
         <v>1000</v>
       </c>
       <c r="D4" t="n">
-        <v>0.722866666666667</v>
+        <v>0.399566666666667</v>
       </c>
       <c r="E4" t="n">
-        <v>0.203062702453687</v>
+        <v>0.24464758826206</v>
       </c>
       <c r="F4" t="n">
-        <v>0.736862353395344</v>
+        <v>0.409898472032269</v>
       </c>
       <c r="G4" t="n">
-        <v>0.697039578299827</v>
+        <v>0.381328966493925</v>
       </c>
       <c r="H4" t="n">
-        <v>0.27708634210852</v>
+        <v>0.599467601729373</v>
       </c>
     </row>
     <row r="5">
@@ -494,19 +494,19 @@
         <v>1000</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7529</v>
+        <v>0.423833333333333</v>
       </c>
       <c r="E5" t="n">
-        <v>0.21101607628595</v>
+        <v>0.271824646856459</v>
       </c>
       <c r="F5" t="n">
-        <v>0.790634227658388</v>
+        <v>0.445305755980129</v>
       </c>
       <c r="G5" t="n">
-        <v>0.705503348604031</v>
+        <v>0.39658500584706</v>
       </c>
       <c r="H5" t="n">
-        <v>0.205108784440059</v>
+        <v>0.554524824516101</v>
       </c>
     </row>
     <row r="6">
@@ -520,19 +520,19 @@
         <v>1000</v>
       </c>
       <c r="D6" t="n">
-        <v>0.754883333333333</v>
+        <v>0.411266666666667</v>
       </c>
       <c r="E6" t="n">
-        <v>0.207515847572325</v>
+        <v>0.27577104170892</v>
       </c>
       <c r="F6" t="n">
-        <v>0.793119388676666</v>
+        <v>0.433230470857993</v>
       </c>
       <c r="G6" t="n">
-        <v>0.706152968699268</v>
+        <v>0.383492187468916</v>
       </c>
       <c r="H6" t="n">
-        <v>0.289721660000934</v>
+        <v>0.615290452646212</v>
       </c>
     </row>
     <row r="7">
@@ -546,19 +546,19 @@
         <v>1000</v>
       </c>
       <c r="D7" t="n">
-        <v>0.75655</v>
+        <v>0.4068</v>
       </c>
       <c r="E7" t="n">
-        <v>0.207413586038743</v>
+        <v>0.265190030768665</v>
       </c>
       <c r="F7" t="n">
-        <v>0.794826229053023</v>
+        <v>0.425361765584156</v>
       </c>
       <c r="G7" t="n">
-        <v>0.708020806642776</v>
+        <v>0.383129216074336</v>
       </c>
       <c r="H7" t="n">
-        <v>0.242824260067734</v>
+        <v>0.59261372738221</v>
       </c>
     </row>
     <row r="8">
@@ -572,19 +572,19 @@
         <v>1000</v>
       </c>
       <c r="D8" t="n">
-        <v>0.729816666666667</v>
+        <v>0.395616666666667</v>
       </c>
       <c r="E8" t="n">
-        <v>0.200069834738037</v>
+        <v>0.243113259845423</v>
       </c>
       <c r="F8" t="n">
-        <v>0.751862714754268</v>
+        <v>0.407932339345466</v>
       </c>
       <c r="G8" t="n">
-        <v>0.698122278068932</v>
+        <v>0.378248314354313</v>
       </c>
       <c r="H8" t="n">
-        <v>0.243271634400263</v>
+        <v>0.591000305775892</v>
       </c>
     </row>
     <row r="9">
@@ -598,19 +598,19 @@
         <v>1000</v>
       </c>
       <c r="D9" t="n">
-        <v>0.734083333333333</v>
+        <v>0.409766666666667</v>
       </c>
       <c r="E9" t="n">
-        <v>0.197328796509049</v>
+        <v>0.244499381850964</v>
       </c>
       <c r="F9" t="n">
-        <v>0.757013228725506</v>
+        <v>0.423389885268391</v>
       </c>
       <c r="G9" t="n">
-        <v>0.700406922182407</v>
+        <v>0.390162385134164</v>
       </c>
       <c r="H9" t="n">
-        <v>0.300842062721306</v>
+        <v>0.607572923991374</v>
       </c>
     </row>
     <row r="10">
@@ -624,19 +624,19 @@
         <v>1000</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7383</v>
+        <v>0.4213</v>
       </c>
       <c r="E10" t="n">
-        <v>0.189583305191636</v>
+        <v>0.249303732904522</v>
       </c>
       <c r="F10" t="n">
-        <v>0.762075620563701</v>
+        <v>0.43350540995284</v>
       </c>
       <c r="G10" t="n">
-        <v>0.703711281418849</v>
+        <v>0.403779762879688</v>
       </c>
       <c r="H10" t="n">
-        <v>0.261220948641257</v>
+        <v>0.57955952319112</v>
       </c>
     </row>
   </sheetData>
